--- a/PCB/同口保护板/生产资料/X2电池保护板-BOM.xlsx
+++ b/PCB/同口保护板/生产资料/X2电池保护板-BOM.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="112">
   <si>
     <r>
       <rPr>
@@ -194,7 +194,7 @@
 Q23</t>
   </si>
   <si>
-    <t>AON2406</t>
+    <t>AON2408</t>
   </si>
   <si>
     <t>MOS(场效应管)</t>
@@ -283,7 +283,13 @@
     <t>2KΩ (2001) ±1%</t>
   </si>
   <si>
-    <t>R13, R20, R21, R22, R27, R29, R34, R37, R40</t>
+    <t>R21, R22, R29, R37, R40</t>
+  </si>
+  <si>
+    <t>680Ω 6800) ±1%</t>
+  </si>
+  <si>
+    <t>R13, R20, R27,R34</t>
   </si>
   <si>
     <t>1KΩ (1001) ±1%</t>
@@ -1504,7 +1510,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1513,6 +1519,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -2072,7 +2081,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="31.7777777777778" customWidth="1"/>
@@ -2085,19 +2094,19 @@
   </cols>
   <sheetData>
     <row r="1" ht="20.4" spans="1:8">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="12" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
@@ -2111,16 +2120,16 @@
       </c>
     </row>
     <row r="2" ht="38.4" spans="1:8">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="13" t="s">
         <v>11</v>
       </c>
       <c r="E2" s="2">
@@ -2134,16 +2143,16 @@
       </c>
     </row>
     <row r="3" ht="19.2" spans="1:8">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="13" t="s">
         <v>15</v>
       </c>
       <c r="E3" s="2">
@@ -2159,16 +2168,16 @@
       </c>
     </row>
     <row r="4" ht="19.2" spans="1:8">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="13" t="s">
         <v>11</v>
       </c>
       <c r="E4" s="2">
@@ -2184,16 +2193,16 @@
       </c>
     </row>
     <row r="5" ht="57.6" spans="1:8">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="13" t="s">
         <v>21</v>
       </c>
       <c r="E5" s="2">
@@ -2211,16 +2220,16 @@
       </c>
     </row>
     <row r="6" ht="19.2" spans="1:8">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="13" t="s">
         <v>26</v>
       </c>
       <c r="E6" s="2">
@@ -2236,16 +2245,16 @@
       </c>
     </row>
     <row r="7" ht="38.4" spans="1:8">
-      <c r="A7" s="12" t="s">
+      <c r="A7" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="C7" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="D7" s="13" t="s">
         <v>30</v>
       </c>
       <c r="E7" s="2">
@@ -2261,16 +2270,16 @@
       </c>
     </row>
     <row r="8" ht="38.4" spans="1:8">
-      <c r="A8" s="12" t="s">
+      <c r="A8" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="D8" s="13" t="s">
+      <c r="D8" s="14" t="s">
         <v>34</v>
       </c>
       <c r="E8" s="2">
@@ -2286,16 +2295,16 @@
       </c>
     </row>
     <row r="9" ht="38.4" spans="1:8">
-      <c r="A9" s="12" t="s">
+      <c r="A9" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="C9" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="D9" s="13" t="s">
         <v>38</v>
       </c>
       <c r="E9" s="2">
@@ -2311,16 +2320,16 @@
       </c>
     </row>
     <row r="10" ht="38.4" spans="1:8">
-      <c r="A10" s="12" t="s">
+      <c r="A10" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="13" t="s">
         <v>38</v>
       </c>
       <c r="E10" s="2">
@@ -2336,16 +2345,16 @@
       </c>
     </row>
     <row r="11" ht="38.4" spans="1:8">
-      <c r="A11" s="12" t="s">
+      <c r="A11" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="C11" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="D11" s="13" t="s">
+      <c r="D11" s="14" t="s">
         <v>45</v>
       </c>
       <c r="E11" s="2">
@@ -2361,16 +2370,16 @@
       </c>
     </row>
     <row r="12" ht="19.2" spans="1:8">
-      <c r="A12" s="12" t="s">
+      <c r="A12" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="C12" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="D12" s="12" t="s">
+      <c r="D12" s="13" t="s">
         <v>38</v>
       </c>
       <c r="E12" s="2">
@@ -2386,16 +2395,16 @@
       </c>
     </row>
     <row r="13" ht="38.4" spans="1:8">
-      <c r="A13" s="12" t="s">
+      <c r="A13" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="C13" s="12" t="s">
+      <c r="C13" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="D13" s="12" t="s">
+      <c r="D13" s="13" t="s">
         <v>52</v>
       </c>
       <c r="E13" s="2">
@@ -2411,16 +2420,16 @@
       </c>
     </row>
     <row r="14" ht="38.4" spans="1:8">
-      <c r="A14" s="12" t="s">
+      <c r="A14" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="B14" s="13" t="s">
+      <c r="B14" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="C14" s="12" t="s">
+      <c r="C14" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D14" s="13" t="s">
         <v>52</v>
       </c>
       <c r="E14" s="2">
@@ -2436,16 +2445,16 @@
       </c>
     </row>
     <row r="15" ht="19.2" spans="1:8">
-      <c r="A15" s="12" t="s">
+      <c r="A15" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="B15" s="12" t="s">
+      <c r="B15" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="C15" s="12" t="s">
+      <c r="C15" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="D15" s="12" t="s">
+      <c r="D15" s="13" t="s">
         <v>52</v>
       </c>
       <c r="E15" s="2">
@@ -2461,16 +2470,16 @@
       </c>
     </row>
     <row r="16" ht="38.4" spans="1:8">
-      <c r="A16" s="12" t="s">
+      <c r="A16" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="B16" s="12" t="s">
+      <c r="B16" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="C16" s="13" t="s">
+      <c r="C16" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="D16" s="12" t="s">
+      <c r="D16" s="13" t="s">
         <v>62</v>
       </c>
       <c r="E16" s="2">
@@ -2486,16 +2495,16 @@
       </c>
     </row>
     <row r="17" ht="19.2" spans="1:8">
-      <c r="A17" s="12" t="s">
+      <c r="A17" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="B17" s="12" t="s">
+      <c r="B17" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="C17" s="12" t="s">
+      <c r="C17" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="D17" s="12" t="s">
+      <c r="D17" s="13" t="s">
         <v>66</v>
       </c>
       <c r="E17" s="2">
@@ -2511,16 +2520,16 @@
       </c>
     </row>
     <row r="18" ht="19.2" spans="1:8">
-      <c r="A18" s="12" t="s">
+      <c r="A18" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="B18" s="12" t="s">
+      <c r="B18" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="C18" s="12" t="s">
+      <c r="C18" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="D18" s="12" t="s">
+      <c r="D18" s="13" t="s">
         <v>62</v>
       </c>
       <c r="E18" s="2">
@@ -2535,21 +2544,21 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="19" ht="19.2" spans="1:8">
-      <c r="A19" s="12" t="s">
+    <row r="19" ht="38.4" spans="1:8">
+      <c r="A19" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="B19" s="12" t="s">
+      <c r="B19" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="C19" s="12" t="s">
+      <c r="C19" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="D19" s="12" t="s">
+      <c r="D19" s="13" t="s">
         <v>62</v>
       </c>
       <c r="E19" s="2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F19" s="2"/>
       <c r="G19" s="2">
@@ -2557,70 +2566,70 @@
       </c>
       <c r="H19" s="2">
         <f t="shared" si="0"/>
-        <v>0.27</v>
-      </c>
-    </row>
-    <row r="20" ht="38.4" spans="1:8">
-      <c r="A20" s="12" t="s">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="20" ht="19.2" spans="1:8">
+      <c r="A20" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="B20" s="12" t="s">
+      <c r="B20" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C20" s="13" t="s">
+      <c r="C20" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="D20" s="12" t="s">
+      <c r="D20" s="2" t="s">
         <v>62</v>
       </c>
       <c r="E20" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F20" s="2"/>
       <c r="G20" s="2">
         <v>0.03</v>
       </c>
       <c r="H20" s="2">
-        <f t="shared" si="0"/>
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="21" ht="19.2" spans="1:8">
-      <c r="A21" s="12" t="s">
+        <f>E20*G20</f>
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="21" ht="38.4" spans="1:8">
+      <c r="A21" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="B21" s="12" t="s">
+      <c r="B21" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="C21" s="12" t="s">
+      <c r="C21" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="D21" s="12" t="s">
+      <c r="D21" s="13" t="s">
         <v>62</v>
       </c>
       <c r="E21" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F21" s="2"/>
       <c r="G21" s="2">
         <v>0.03</v>
       </c>
       <c r="H21" s="2">
-        <f t="shared" si="0"/>
-        <v>0.03</v>
+        <f>E21*G21</f>
+        <v>0.15</v>
       </c>
     </row>
     <row r="22" ht="19.2" spans="1:8">
-      <c r="A22" s="12" t="s">
+      <c r="A22" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="B22" s="12" t="s">
+      <c r="B22" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="C22" s="12" t="s">
+      <c r="C22" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="D22" s="12" t="s">
+      <c r="D22" s="13" t="s">
         <v>62</v>
       </c>
       <c r="E22" s="2">
@@ -2631,296 +2640,321 @@
         <v>0.03</v>
       </c>
       <c r="H22" s="2">
-        <f t="shared" si="0"/>
+        <f>E22*G22</f>
         <v>0.03</v>
       </c>
     </row>
     <row r="23" ht="19.2" spans="1:8">
-      <c r="A23" s="12" t="s">
+      <c r="A23" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="B23" s="12" t="s">
+      <c r="B23" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="C23" s="12" t="s">
+      <c r="C23" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="D23" s="12" t="s">
+      <c r="D23" s="13" t="s">
         <v>62</v>
       </c>
       <c r="E23" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F23" s="2"/>
       <c r="G23" s="2">
         <v>0.03</v>
       </c>
       <c r="H23" s="2">
-        <f t="shared" si="0"/>
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="24" ht="38.4" spans="1:8">
-      <c r="A24" s="12" t="s">
+        <f>E23*G23</f>
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="24" ht="19.2" spans="1:8">
+      <c r="A24" s="13" t="s">
         <v>79</v>
       </c>
       <c r="B24" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="C24" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="C24" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="D24" s="12" t="s">
+      <c r="D24" s="13" t="s">
         <v>62</v>
       </c>
       <c r="E24" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F24" s="2"/>
       <c r="G24" s="2">
-        <v>0.1</v>
+        <v>0.03</v>
       </c>
       <c r="H24" s="2">
-        <f t="shared" si="0"/>
-        <v>0.1</v>
+        <f>E24*G24</f>
+        <v>0.12</v>
       </c>
     </row>
     <row r="25" ht="38.4" spans="1:8">
-      <c r="A25" s="12" t="s">
+      <c r="A25" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="B25" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="B25" s="13" t="s">
+      <c r="C25" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="C25" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="D25" s="12" t="s">
-        <v>85</v>
+      <c r="D25" s="13" t="s">
+        <v>62</v>
       </c>
       <c r="E25" s="2">
         <v>1</v>
       </c>
       <c r="F25" s="2"/>
       <c r="G25" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="H25" s="2">
+        <f>E25*G25</f>
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="26" ht="38.4" spans="1:8">
+      <c r="A26" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="B26" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="C26" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="D26" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="E26" s="2">
+        <v>1</v>
+      </c>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2">
         <v>3.5</v>
       </c>
-      <c r="H25" s="2">
-        <f t="shared" si="0"/>
+      <c r="H26" s="2">
+        <f>E26*G26</f>
         <v>3.5</v>
       </c>
     </row>
-    <row r="26" ht="43" customHeight="1" spans="1:8">
-      <c r="A26" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="C26" s="4" t="s">
+    <row r="27" ht="43" customHeight="1" spans="1:8">
+      <c r="A27" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="B27" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="E26" s="4">
+      <c r="C27" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="E27" s="5">
         <v>2</v>
       </c>
-      <c r="F26" s="6"/>
-      <c r="G26" s="4">
+      <c r="F27" s="7"/>
+      <c r="G27" s="5">
         <v>0.7</v>
       </c>
-      <c r="H26" s="2">
-        <f t="shared" ref="H26:H32" si="1">E26*G26</f>
+      <c r="H27" s="2">
+        <f t="shared" ref="H27:H33" si="1">E27*G27</f>
         <v>1.4</v>
       </c>
     </row>
-    <row r="27" ht="40.8" spans="1:8">
-      <c r="A27" s="4" t="s">
+    <row r="28" ht="40.8" spans="1:8">
+      <c r="A28" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="C28" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="E27" s="4">
+      <c r="D28" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="E28" s="5">
         <v>5</v>
       </c>
-      <c r="F27" s="6"/>
-      <c r="G27" s="4">
+      <c r="F28" s="7"/>
+      <c r="G28" s="5">
         <v>0.482</v>
       </c>
-      <c r="H27" s="2">
+      <c r="H28" s="2">
         <f t="shared" si="1"/>
         <v>2.41</v>
       </c>
     </row>
-    <row r="28" ht="40.8" spans="1:8">
-      <c r="A28" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="D28" s="4" t="s">
+    <row r="29" ht="40.8" spans="1:8">
+      <c r="A29" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="E28" s="4">
+      <c r="B29" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="E29" s="5">
         <v>4</v>
       </c>
-      <c r="F28" s="6"/>
-      <c r="G28" s="4">
+      <c r="F29" s="7"/>
+      <c r="G29" s="5">
         <v>0.297</v>
       </c>
-      <c r="H28" s="2">
+      <c r="H29" s="2">
         <f t="shared" si="1"/>
         <v>1.188</v>
       </c>
     </row>
-    <row r="29" ht="40.8" spans="1:8">
-      <c r="A29" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="D29" s="4" t="s">
+    <row r="30" ht="40.8" spans="1:8">
+      <c r="A30" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="E29" s="4">
+      <c r="B30" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="E30" s="5">
         <v>1</v>
       </c>
-      <c r="F29" s="6"/>
-      <c r="G29" s="4">
+      <c r="F30" s="7"/>
+      <c r="G30" s="5">
         <v>0.403</v>
       </c>
-      <c r="H29" s="2">
+      <c r="H30" s="2">
         <f t="shared" si="1"/>
         <v>0.403</v>
       </c>
     </row>
-    <row r="30" ht="40.8" spans="1:8">
-      <c r="A30" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="D30" s="4" t="s">
+    <row r="31" ht="40.8" spans="1:8">
+      <c r="A31" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="E30" s="4">
+      <c r="B31" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="E31" s="5">
         <v>3</v>
       </c>
-      <c r="F30" s="6"/>
-      <c r="G30" s="4">
+      <c r="F31" s="7"/>
+      <c r="G31" s="5">
         <v>0.288</v>
       </c>
-      <c r="H30" s="2">
+      <c r="H31" s="2">
         <f t="shared" si="1"/>
         <v>0.864</v>
       </c>
     </row>
-    <row r="31" ht="40.8" spans="1:8">
-      <c r="A31" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="D31" s="4" t="s">
+    <row r="32" ht="40.8" spans="1:8">
+      <c r="A32" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="E31" s="4">
+      <c r="B32" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="E32" s="5">
         <v>1</v>
       </c>
-      <c r="F31" s="6"/>
-      <c r="G31" s="4">
+      <c r="F32" s="7"/>
+      <c r="G32" s="5">
         <v>0.546</v>
       </c>
-      <c r="H31" s="2">
+      <c r="H32" s="2">
         <f t="shared" si="1"/>
         <v>0.546</v>
       </c>
     </row>
-    <row r="32" ht="40.8" spans="1:8">
-      <c r="A32" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="D32" s="4" t="s">
+    <row r="33" ht="40.8" spans="1:8">
+      <c r="A33" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="E32" s="4">
+      <c r="B33" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="E33" s="5">
         <v>5</v>
       </c>
-      <c r="F32" s="6"/>
-      <c r="G32" s="4">
+      <c r="F33" s="7"/>
+      <c r="G33" s="5">
         <v>0.236</v>
       </c>
-      <c r="H32" s="2">
+      <c r="H33" s="2">
         <f t="shared" si="1"/>
         <v>1.18</v>
       </c>
     </row>
-    <row r="33" ht="20.4" spans="1:8">
-      <c r="A33" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="B33" s="8"/>
-      <c r="C33" s="8"/>
-      <c r="D33" s="8"/>
-      <c r="E33" s="8"/>
-      <c r="F33" s="8"/>
-      <c r="G33" s="9">
-        <f>SUM(H2:H32)</f>
+    <row r="34" ht="20.4" spans="1:8">
+      <c r="A34" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="B34" s="9"/>
+      <c r="C34" s="9"/>
+      <c r="D34" s="9"/>
+      <c r="E34" s="9"/>
+      <c r="F34" s="9"/>
+      <c r="G34" s="10">
+        <f>SUM(H2:H33)</f>
         <v>244.51</v>
       </c>
-      <c r="H33" s="9"/>
-    </row>
-    <row r="34" ht="22.2" spans="1:8">
-      <c r="A34" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="B34" s="10"/>
-      <c r="C34" s="10"/>
-      <c r="D34" s="10"/>
-      <c r="E34" s="10">
-        <f>SUM(E2:E32)</f>
+      <c r="H34" s="10"/>
+    </row>
+    <row r="35" ht="22.2" spans="1:8">
+      <c r="A35" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="B35" s="11"/>
+      <c r="C35" s="11"/>
+      <c r="D35" s="11"/>
+      <c r="E35" s="11">
+        <f>SUM(E2:E33)</f>
         <v>107</v>
       </c>
-      <c r="F34" s="10"/>
-      <c r="G34" s="10"/>
-      <c r="H34" s="10"/>
+      <c r="F35" s="11"/>
+      <c r="G35" s="11"/>
+      <c r="H35" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A33:F33"/>
-    <mergeCell ref="G33:H33"/>
-    <mergeCell ref="A34:D34"/>
-    <mergeCell ref="E34:H34"/>
+    <mergeCell ref="A34:F34"/>
+    <mergeCell ref="G34:H34"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="E35:H35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
